--- a/artfynd/A 35239-2026 artfynd.xlsx
+++ b/artfynd/A 35239-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136193841</v>
       </c>
       <c r="B2" t="n">
-        <v>92102</v>
+        <v>92105</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136481036</v>
       </c>
       <c r="B3" t="n">
-        <v>92498</v>
+        <v>92501</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35239-2026 artfynd.xlsx
+++ b/artfynd/A 35239-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136193841</v>
       </c>
       <c r="B2" t="n">
-        <v>92105</v>
+        <v>92106</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136481036</v>
       </c>
       <c r="B3" t="n">
-        <v>92501</v>
+        <v>92502</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35239-2026 artfynd.xlsx
+++ b/artfynd/A 35239-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136193841</v>
       </c>
       <c r="B2" t="n">
-        <v>92106</v>
+        <v>92111</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136481036</v>
       </c>
       <c r="B3" t="n">
-        <v>92502</v>
+        <v>92507</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35239-2026 artfynd.xlsx
+++ b/artfynd/A 35239-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136193841</v>
       </c>
       <c r="B2" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136481036</v>
       </c>
       <c r="B3" t="n">
-        <v>92507</v>
+        <v>92509</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35239-2026 artfynd.xlsx
+++ b/artfynd/A 35239-2026 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>136481036</v>
       </c>
       <c r="B3" t="n">
-        <v>92509</v>
+        <v>92511</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35239-2026 artfynd.xlsx
+++ b/artfynd/A 35239-2026 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>136481036</v>
       </c>
       <c r="B3" t="n">
-        <v>92511</v>
+        <v>92513</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35239-2026 artfynd.xlsx
+++ b/artfynd/A 35239-2026 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>136481036</v>
       </c>
       <c r="B3" t="n">
-        <v>92513</v>
+        <v>92514</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35239-2026 artfynd.xlsx
+++ b/artfynd/A 35239-2026 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>136481036</v>
       </c>
       <c r="B3" t="n">
-        <v>92514</v>
+        <v>92520</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35239-2026 artfynd.xlsx
+++ b/artfynd/A 35239-2026 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>136481036</v>
       </c>
       <c r="B3" t="n">
-        <v>92520</v>
+        <v>92524</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
